--- a/GameConfig/Datas/global_config.xlsx
+++ b/GameConfig/Datas/global_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\FreshGuard\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF08D10-D314-4C0C-A076-DE6119FEB52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54141DF2-5210-426A-9C53-4B5776BCBE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="1035" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>TargetHp_目标点默认血量值</t>
         </r>
@@ -44,6 +46,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>NormalSpeed_普通能源球基础恒定速度</t>
         </r>
@@ -56,6 +60,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RageSpeed_暴走能源球基础恒定速度；由原虚化速度字段沿用</t>
         </r>
@@ -68,6 +74,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>NormalBounceAngleRange_普通能源球反弹随机修正范围</t>
         </r>
@@ -80,6 +88,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RageBounceAngleRange_暴走能源球反弹随机修正范围；由原虚化字段沿用</t>
         </r>
@@ -92,6 +102,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>NormalAntiLoopProfile_普通能源球反弹方向与0°、90°、180°、270°之间允许的最小角度差</t>
         </r>
@@ -104,6 +116,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RageAntiLoopProfile_暴走能源球反弹方向与四个轴向角度之间允许的最小角度差</t>
         </r>
@@ -116,6 +130,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RobotTriggerInterval_每个机器人实例独立维护，所有能源球共享该机器人的触发间隔</t>
         </r>
@@ -128,6 +144,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>GlassTriggerInterval_每块七彩玻璃实例独立维护，所有能源球共享该玻璃的碰撞间隔</t>
         </r>
@@ -140,6 +158,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ComboTriggerCount_进入暴走状态所需的连续有效碰撞数</t>
         </r>
@@ -152,6 +172,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -164,6 +186,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -176,6 +200,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -188,6 +214,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -200,6 +228,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RageDurationSec_暴走状态持续秒数</t>
         </r>
@@ -212,6 +242,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RageStayInterval_暴走能源球持续位于同一机器人内部时再次尝试行动的周期；由原虚化字段沿用</t>
         </r>
@@ -224,6 +256,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>DragSpeedRate_玩家拖拽或AI移动预告期间，普通能源球的速度倍率</t>
         </r>
@@ -236,6 +270,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>LowSpeedThreshold_进入低速异常计时的速度阈值</t>
         </r>
@@ -248,6 +284,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>LowSpeedDuration_持续低于阈值后触发重发的时间</t>
         </r>
@@ -260,6 +298,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>NoInteractionDuration_未产生有效互动后触发重发的时间</t>
         </r>
@@ -272,6 +312,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>LaunchDirectionRange_开局与异常重发时允许抽取的发射方向范围；开局双方共享抽取结果，异常重发分别独立抽取</t>
         </r>
@@ -284,6 +326,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>BattleInitialSP_开局可支配SP为20；SP当前仅为战斗资源代称</t>
         </r>
@@ -296,6 +340,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopSlotCount_首批及每次刷新生成的商品槽数量</t>
         </r>
@@ -308,6 +354,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>NormalEnemyKillSP_击败普通敌人增加4SP；SP当前仅为战斗资源代称</t>
         </r>
@@ -320,6 +368,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>EliteEnemyKillSP_击败精英增加20SP；SP当前仅为战斗资源代称</t>
         </r>
@@ -332,6 +382,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>BossKillSP_击败Boss增加50SP；SP当前仅为战斗资源代称</t>
         </r>
@@ -344,6 +396,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>NormalGlassBreakSP_击碎普通玻璃增加10SP；SP当前仅为战斗资源代称</t>
         </r>
@@ -356,6 +410,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ColoredGlassBreakSP_击碎彩色玻璃增加10SP；SP当前仅为战斗资源代称</t>
         </r>
@@ -368,6 +424,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopRefreshPrice_每次刷新固定消耗5SP；首批商品免费生成</t>
         </r>
@@ -380,6 +438,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopLv2RateAfterInitial_首批商品固定1星；其后每个商品槽独立生成2星机器人的概率</t>
         </r>
@@ -392,6 +452,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopRepeatRerollLimit_新旧两批机器人ID多重集合相同时最多重抽次数</t>
         </r>
@@ -404,6 +466,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -416,6 +480,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -428,6 +494,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ComboBreakSec_有效碰撞间隔超过该秒数时Combo中断</t>
         </r>
@@ -440,6 +508,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RageExtraBallCount_进入暴走后额外生成的能源球数量；主球固定1颗，总数为5颗</t>
         </r>
@@ -452,6 +522,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopQuality2Lv1Price_绿色机器人（QualityID=2）的1星购买价格</t>
         </r>
@@ -464,6 +536,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopQuality3Lv1Price_蓝色机器人（QualityID=3）的1星购买价格</t>
         </r>
@@ -476,6 +550,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopQuality4Lv1Price_紫色机器人（QualityID=4）的1星购买价格</t>
         </r>
@@ -488,6 +564,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopQuality5Lv1Price_橙色机器人（QualityID=5）的1星购买价格</t>
         </r>
@@ -500,6 +578,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>ShopQuality6Lv1Price_红色机器人（QualityID=6）的1星购买价格</t>
         </r>
@@ -512,6 +592,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -524,6 +606,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -536,6 +620,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>肉鸽自动选择时间</t>
         </r>
@@ -548,6 +634,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>已有同Build后的候选权重倍率</t>
         </r>
@@ -560,6 +648,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -572,6 +662,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -584,6 +676,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>预留（参考表未配置数值）</t>
         </r>
@@ -596,6 +690,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>CycleWave_一个 Cycle 包含的波数</t>
         </r>
@@ -608,6 +704,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>RageReentryBlockSec_暴走再入保护</t>
         </r>
@@ -620,6 +718,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>NormalSpeedMaxRate_普通球速上限</t>
         </r>
@@ -632,6 +732,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>StaminaMax_体力上限</t>
         </r>
@@ -644,6 +746,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>StaminaRecoverIntervalMin_体力恢复间隔（分钟）</t>
         </r>
@@ -794,9 +898,6 @@
     <t>ComboBreakSec_有效碰撞间隔超过该秒数时Combo中断</t>
   </si>
   <si>
-    <t>RageExtraBallCount_进入暴走后额外生成的能源球数量；主球固定1颗，总数为5颗</t>
-  </si>
-  <si>
     <t>ShopQuality2Lv1Price_绿色机器人（QualityID=2）的1星购买价格</t>
   </si>
   <si>
@@ -831,6 +932,10 @@
   </si>
   <si>
     <t>StaminaRecoverIntervalMin_体力恢复间隔（分钟）</t>
+  </si>
+  <si>
+    <t>RageExtraBallCount_进入暴走后额外生成的能源球数量</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -853,24 +958,28 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -878,6 +987,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -885,6 +995,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -892,6 +1003,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -899,6 +1011,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -906,12 +1019,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -919,6 +1034,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -926,6 +1042,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -933,12 +1050,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -946,42 +1065,49 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF777777"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1455,7 +1581,7 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1590,6 +1716,60 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3886200</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11FE41B3-BBF2-1A3C-6875-866F510A162D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -2282,11 +2462,11 @@
         <v>35</v>
       </c>
       <c r="C40" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2298,7 +2478,7 @@
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2310,7 +2490,7 @@
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2322,7 +2502,7 @@
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2334,7 +2514,7 @@
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2346,7 +2526,7 @@
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2378,7 +2558,7 @@
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2390,7 +2570,7 @@
       </c>
       <c r="D49" s="10"/>
       <c r="E49" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2432,7 +2612,7 @@
       </c>
       <c r="D53" s="10"/>
       <c r="E53" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2444,7 +2624,7 @@
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2456,7 +2636,7 @@
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2468,7 +2648,7 @@
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2480,7 +2660,7 @@
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/global_config.xlsx
+++ b/GameConfig/Datas/global_config.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\FreshGuard\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\FreshGuard\UnityProject\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E59057A-7342-4EE7-8B7D-390FB05AE61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,12 +32,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>User</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -51,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -77,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="B9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -116,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -142,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="B14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -155,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="B15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -168,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -181,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="B17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -194,7 +193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="B18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -207,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -220,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="B20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -233,7 +232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="B21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -246,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -259,7 +258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="B23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -272,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+    <comment ref="B24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -285,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -298,7 +297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+    <comment ref="B26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -311,7 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+    <comment ref="B27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -324,7 +323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+    <comment ref="B28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -337,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
+    <comment ref="B29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -350,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
+    <comment ref="B30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -363,7 +362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
+    <comment ref="B31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -376,7 +375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
+    <comment ref="B32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -389,7 +388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
+    <comment ref="B33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -402,7 +401,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
+    <comment ref="B34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -415,7 +414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
+    <comment ref="B35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -428,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
+    <comment ref="B36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -441,7 +440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
+    <comment ref="B37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -454,7 +453,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
+    <comment ref="B38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -467,7 +466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
+    <comment ref="B39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -480,7 +479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B40" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
+    <comment ref="B40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -493,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
+    <comment ref="B41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -506,7 +505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
+    <comment ref="B42" authorId="0">
       <text>
         <r>
           <rPr>
@@ -519,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
+    <comment ref="B43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -532,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
+    <comment ref="B44" authorId="0">
       <text>
         <r>
           <rPr>
@@ -545,7 +544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
+    <comment ref="B45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -558,7 +557,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
+    <comment ref="B46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -571,7 +570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
+    <comment ref="B47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -584,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B000000}">
+    <comment ref="B48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -597,7 +596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C000000}">
+    <comment ref="B49" authorId="0">
       <text>
         <r>
           <rPr>
@@ -610,7 +609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D000000}">
+    <comment ref="B50" authorId="0">
       <text>
         <r>
           <rPr>
@@ -623,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002E000000}">
+    <comment ref="B51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -636,7 +635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002F000000}">
+    <comment ref="B52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -649,7 +648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000030000000}">
+    <comment ref="B53" authorId="0">
       <text>
         <r>
           <rPr>
@@ -662,7 +661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000031000000}">
+    <comment ref="B54" authorId="0">
       <text>
         <r>
           <rPr>
@@ -675,7 +674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000032000000}">
+    <comment ref="B55" authorId="0">
       <text>
         <r>
           <rPr>
@@ -688,7 +687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000033000000}">
+    <comment ref="B56" authorId="0">
       <text>
         <r>
           <rPr>
@@ -701,7 +700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000034000000}">
+    <comment ref="B57" authorId="0">
       <text>
         <r>
           <rPr>
@@ -799,6 +798,18 @@
     <t>ComboTriggerCount：进入暴走所需连续有效机器人反弹次数（正整数）【本次接入】不再固定50次。玻璃、墙壁不计Combo。</t>
   </si>
   <si>
+    <t>反弹后的增加的速度</t>
+  </si>
+  <si>
+    <t>速度衰减的时间</t>
+  </si>
+  <si>
+    <t>和墙体碰撞是否有加速</t>
+  </si>
+  <si>
+    <t>和机器人碰撞是否有加速</t>
+  </si>
+  <si>
     <t>RageDurationSec：暴走持续时间（秒，正数）【已接入】暂停战斗期间不消耗此时间。</t>
   </si>
   <si>
@@ -905,29 +916,19 @@
   </si>
   <si>
     <t>StaminaRecoverIntervalMin：主界面恢复1点体力所需分钟数（正整数）【已接入】启动时读取，保存时间用于离线恢复；读取失败回退5分钟并告警。</t>
-  </si>
-  <si>
-    <t>反弹后的速度</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>速度衰减的时间</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>和墙体碰撞是否有加速</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>和机器人碰撞是否有加速</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -954,9 +955,159 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF777777"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -964,20 +1115,8 @@
       <name val="等线"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF777777"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -992,12 +1131,186 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1020,32 +1333,265 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1061,27 +1607,72 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
-    <cellStyle name="着色 1" xfId="2" builtinId="29"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1095,15 +1686,9 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1077" name="Text Box 53" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1077" name="Text Box 53" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1321,694 +1906,694 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="13" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="1" customWidth="1"/>
     <col min="5" max="5" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:5">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="7">
+    <row r="6" ht="48" customHeight="1" spans="1:5">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>100</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="7">
+    <row r="7" ht="48" customHeight="1" spans="1:5">
+      <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>3</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="7">
+    <row r="8" ht="48" customHeight="1" spans="1:5">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>6</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="7">
+    <row r="9" ht="48" customHeight="1" spans="1:5">
+      <c r="B9" s="6">
         <v>4</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>6</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="7">
+    <row r="10" ht="48" customHeight="1" spans="1:5">
+      <c r="B10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>8</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="7">
+    <row r="11" ht="48" customHeight="1" spans="1:5">
+      <c r="B11" s="6">
         <v>6</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>7</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="7">
+    <row r="12" ht="48" customHeight="1" spans="1:5">
+      <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>7</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="8"/>
+      <c r="E12" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="7">
+    <row r="13" ht="48" customHeight="1" spans="1:5">
+      <c r="B13" s="6">
         <v>8</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>0.25</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10" t="s">
+      <c r="D13" s="8"/>
+      <c r="E13" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="7">
+    <row r="14" ht="48" customHeight="1" spans="1:5">
+      <c r="B14" s="6">
         <v>9</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>0.15</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="7">
+    <row r="15" ht="48" customHeight="1" spans="1:5">
+      <c r="B15" s="6">
         <v>10</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>50</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="7">
+    <row r="16" ht="48" customHeight="1" spans="1:5">
+      <c r="B16" s="6">
         <v>11</v>
       </c>
-      <c r="C16" s="8">
-        <v>4</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="1" t="s">
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" spans="2:5">
+      <c r="B17" s="6">
+        <v>12</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" spans="2:5">
+      <c r="B18" s="6">
+        <v>13</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="2:5">
+      <c r="B19" s="6">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" spans="2:5">
+      <c r="B20" s="6">
+        <v>15</v>
+      </c>
+      <c r="C20" s="7">
+        <v>6</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" spans="2:5">
+      <c r="B21" s="6">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" spans="2:5">
+      <c r="B22" s="6">
+        <v>17</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" spans="2:5">
+      <c r="B23" s="6">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" spans="2:5">
+      <c r="B24" s="6">
+        <v>19</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" spans="2:5">
+      <c r="B25" s="6">
+        <v>20</v>
+      </c>
+      <c r="C25" s="7">
+        <v>5</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" spans="2:5">
+      <c r="B26" s="6">
+        <v>21</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" spans="2:5">
+      <c r="B27" s="6">
+        <v>22</v>
+      </c>
+      <c r="C27" s="7">
+        <v>20</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" spans="2:5">
+      <c r="B28" s="6">
+        <v>23</v>
+      </c>
+      <c r="C28" s="7">
+        <v>3</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" spans="2:5">
+      <c r="B29" s="6">
+        <v>24</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" ht="48" customHeight="1" spans="2:5">
+      <c r="B30" s="6">
+        <v>25</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" ht="48" customHeight="1" spans="2:5">
+      <c r="B31" s="6">
+        <v>26</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" ht="48" customHeight="1" spans="2:5">
+      <c r="B32" s="6">
+        <v>27</v>
+      </c>
+      <c r="C32" s="7">
+        <v>2</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1" spans="2:5">
+      <c r="B33" s="6">
+        <v>28</v>
+      </c>
+      <c r="C33" s="7">
+        <v>2</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1" spans="2:5">
+      <c r="B34" s="6">
+        <v>29</v>
+      </c>
+      <c r="C34" s="7">
+        <v>5</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1" spans="2:5">
+      <c r="B35" s="6">
+        <v>30</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1" spans="2:5">
+      <c r="B36" s="6">
+        <v>31</v>
+      </c>
+      <c r="C36" s="7">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1" spans="2:5">
+      <c r="B37" s="6">
+        <v>32</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1" spans="2:5">
+      <c r="B38" s="6">
+        <v>33</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1" spans="2:5">
+      <c r="B39" s="6">
+        <v>34</v>
+      </c>
+      <c r="C39" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" spans="2:5">
+      <c r="B40" s="6">
+        <v>35</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1" spans="2:5">
+      <c r="B41" s="6">
+        <v>36</v>
+      </c>
+      <c r="C41" s="7">
+        <v>6</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" spans="2:5">
+      <c r="B42" s="6">
+        <v>37</v>
+      </c>
+      <c r="C42" s="7">
+        <v>8</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1" spans="2:5">
+      <c r="B43" s="6">
+        <v>38</v>
+      </c>
+      <c r="C43" s="7">
+        <v>12</v>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1" spans="2:5">
+      <c r="B44" s="6">
+        <v>39</v>
+      </c>
+      <c r="C44" s="7">
+        <v>16</v>
+      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" spans="2:5">
+      <c r="B45" s="6">
+        <v>40</v>
+      </c>
+      <c r="C45" s="7">
+        <v>20</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1" spans="2:5">
+      <c r="B46" s="6">
+        <v>41</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1" spans="2:5">
+      <c r="B47" s="6">
+        <v>42</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1" spans="2:5">
+      <c r="B48" s="6">
+        <v>43</v>
+      </c>
+      <c r="C48" s="7">
+        <v>5</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1" spans="2:5">
+      <c r="B49" s="6">
+        <v>44</v>
+      </c>
+      <c r="C49" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1" spans="2:5">
+      <c r="B50" s="6">
+        <v>45</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1" spans="2:5">
+      <c r="B51" s="6">
+        <v>46</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1" spans="2:5">
+      <c r="B52" s="6">
+        <v>47</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1" spans="2:5">
+      <c r="B53" s="6">
+        <v>48</v>
+      </c>
+      <c r="C53" s="7">
+        <v>10</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1" spans="2:5">
+      <c r="B54" s="6">
+        <v>49</v>
+      </c>
+      <c r="C54" s="7">
+        <v>5</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="7">
-        <v>12</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="1" t="s">
+    <row r="55" ht="48" customHeight="1" spans="2:5">
+      <c r="B55" s="6">
+        <v>50</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="D55" s="8"/>
+      <c r="E55" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="7">
-        <v>13</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="1" t="s">
+    <row r="56" ht="48" customHeight="1" spans="2:5">
+      <c r="B56" s="6">
+        <v>51</v>
+      </c>
+      <c r="C56" s="7">
+        <v>30</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="7">
-        <v>14</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="1" t="s">
+    <row r="57" ht="48" customHeight="1" spans="2:5">
+      <c r="B57" s="6">
+        <v>52</v>
+      </c>
+      <c r="C57" s="7">
+        <v>5</v>
+      </c>
+      <c r="D57" s="8"/>
+      <c r="E57" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="7">
-        <v>15</v>
-      </c>
-      <c r="C20" s="8">
-        <v>6</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="7">
-        <v>16</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="7">
-        <v>17</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="7">
-        <v>18</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="7">
-        <v>19</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="7">
-        <v>20</v>
-      </c>
-      <c r="C25" s="8">
-        <v>5</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="7">
-        <v>21</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="7">
-        <v>22</v>
-      </c>
-      <c r="C27" s="8">
-        <v>20</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="7">
-        <v>23</v>
-      </c>
-      <c r="C28" s="8">
-        <v>3</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="7">
-        <v>24</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="7">
-        <v>25</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="7">
-        <v>26</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="7">
-        <v>27</v>
-      </c>
-      <c r="C32" s="8">
-        <v>2</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="7">
-        <v>28</v>
-      </c>
-      <c r="C33" s="8">
-        <v>2</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="7">
-        <v>29</v>
-      </c>
-      <c r="C34" s="8">
-        <v>5</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="7">
-        <v>30</v>
-      </c>
-      <c r="C35" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="7">
-        <v>31</v>
-      </c>
-      <c r="C36" s="8">
-        <v>10</v>
-      </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="7">
-        <v>32</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="7">
-        <v>33</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="7">
-        <v>34</v>
-      </c>
-      <c r="C39" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="7">
-        <v>35</v>
-      </c>
-      <c r="C40" s="8">
-        <v>2</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="7">
-        <v>36</v>
-      </c>
-      <c r="C41" s="8">
-        <v>6</v>
-      </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="7">
-        <v>37</v>
-      </c>
-      <c r="C42" s="8">
-        <v>8</v>
-      </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="7">
-        <v>38</v>
-      </c>
-      <c r="C43" s="8">
-        <v>12</v>
-      </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="7">
-        <v>39</v>
-      </c>
-      <c r="C44" s="8">
-        <v>16</v>
-      </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="7">
-        <v>40</v>
-      </c>
-      <c r="C45" s="8">
-        <v>20</v>
-      </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="7">
-        <v>41</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="7">
-        <v>42</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="7">
-        <v>43</v>
-      </c>
-      <c r="C48" s="8">
-        <v>5</v>
-      </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="7">
-        <v>44</v>
-      </c>
-      <c r="C49" s="8">
-        <v>1.4</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="7">
-        <v>45</v>
-      </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="7">
-        <v>46</v>
-      </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="7">
-        <v>47</v>
-      </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="7">
-        <v>48</v>
-      </c>
-      <c r="C53" s="8">
-        <v>10</v>
-      </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="7">
-        <v>49</v>
-      </c>
-      <c r="C54" s="8">
-        <v>5</v>
-      </c>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="7">
-        <v>50</v>
-      </c>
-      <c r="C55" s="8">
-        <v>1.75</v>
-      </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="7">
-        <v>51</v>
-      </c>
-      <c r="C56" s="8">
-        <v>30</v>
-      </c>
-      <c r="D56" s="9"/>
-      <c r="E56" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="7">
-        <v>52</v>
-      </c>
-      <c r="C57" s="8">
-        <v>5</v>
-      </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>